--- a/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
+++ b/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -502,6 +502,742 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ALQUILER BUS 55 PLAZAS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Empresa ya contactada (misma del reto anterior, nombre sin confirmar)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>55 asientos, presupuesto con descuento negociado</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Urgente (presupuesto vence a los 15 días de recibido, 24 ago)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>~1.197€ (sin confirmar exacto, Marco lo dijo con dudas)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>A definir con Administración</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Correo con presupuesto ya recibido por Mariano, falta abrirlo y confirmar cifra exacta</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RADIOS VHF GRAN ALCANCE (nuevas)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Por confirmar — Marco va a reconsultar a la empresa de radios</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sin definir</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Deben servir en montaña (10km+ con varias montañas de por medio), resistentes al agua — las alquiladas el reto anterior NO sirvieron</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Urgente, sin fecha exacta</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Marco le escribe a la empresa explicando que las anteriores no funcionaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ETIQUETAS/PEGATINAS DE PROVISIONES</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Proveedor de Julio (el más barato cotizado, tiene el link)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Paquete de 100</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Para pegar en las bolsas de provisiones armadas</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sin definir</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>~31,90€ (puede subir 2-3€ vs. la vez pasada)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Discrepancia sin resolver: faltan 39 según el plan de 65 bolsas nuevas, pero el inventario general pide 90 en total — no se resolvió en la llamada</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BOLSAS VACÍAS PARA PROVISIONES</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Amazon (junto con bolsas de basura negras, para un solo pedido)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Paquete de 100</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Para armar las bolsas de provisiones nuevas</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sin definir</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Hay 34 actuales — comprar de más porque algunas vienen malas/no se pegan bien</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PALA METÁLICA PARA CARBÓN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Amazon o Bricomart/Obramar (a definir)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Para mover el carbón de la parrilla — la pala de la iglesia está destinada a otra cosa (agujero de la cruz)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sin definir</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Julio manda el link elegido para que Mariano arme el presupuesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAÑAS PARA ANTORCHAS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Contacto de Jonathan (vía Marco Guanuchi)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1 paquete de 12</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Cañas de bambú para las antorchas — se corta a la mitad y se mete la antorcha</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ya coordinado, se retira el domingo</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>~23-24€</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>A confirmar quién paga y si se reembolsa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Resuelto (coordinación)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>YA COORDINADO — no hace falta el link de Amazon que había mandado el pastor, ese era para las antorchas en sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PLATOS CENA DEL REY (con logo grabado)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tedi</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Faltan 4 de las 52 necesarias (hay 48) — son de madera/tronquito</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sin definir</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>~12€ (no confirmado si es por unidad o total)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>David confirma stock real en la web de Tedi antes de comprar. Richard graba el nombre DESPUÉS de comprarlos, no antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CINTA REFLECTANTE NOCTURNA PLATEADA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Obramar o Leroy Merlin (a confirmar)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sin definir</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Material plástico gris que se ilumina de noche, para marcar el camino/rutas — NO es precinto normal</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sin definir</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>No se consiguió el reto anterior por buscarla a último momento</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ALARGADOR ELÉCTRICO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Administración (Juliana)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Uno para el rótulo luminoso, otro alargador general</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sin definir</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Probar primero el alargador amarillo grande que ya tienen — puede no estar funcionando</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CAMIÓN CAJA ABIERTA / PICK-UP 4x4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Por confirmar — un lugar en Valencia manda presupuesto el 25 ago</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Debe soportar 1.000kg. Mariano prefiere pick-up 4x4 (Ford Ranger/Hilux/Amarok/Isuzu) por sobre un camión largo tipo Iveco — más manejable en tramos difíciles de montaña</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Presupuesto llega el 25 ago a primera hora</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>David también evalúa opciones en Alicante/Castellón si en Valencia no aparece pick-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FURGONETA (préstamo, no compra)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Jefferson</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Julio confirma con Jefferson si puede prestar furgoneta Y camión juntos — Mateo (dueño del otro camión posible) tiene el suyo con roturas frecuentes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sin definir</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>No es compra, es préstamo — se incluye acá para no perder el seguimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PEGATINA RUGE CON NOMBRE Y TALLA (impresa)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Levis</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sin definir (por senderista)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Nombre + talla + logo Ruge, hecha en computadora/impresora (se descartó escribir a mano con rotulador)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sin definir, Julio consulta mañana 25 ago</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>A confirmar si entra en el mismo presupuesto que el rótulo luminoso</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Julio pide cotización y tiempos de entrega a Levis</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RÓTULO LUMINOSO INFERIOR "ESPAÑA"</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Levis</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mismo ancho que el rótulo grande ya existente, más angosto en largo</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sin definir, Julio consulta mañana 25 ago</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>A confirmar</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Marco Guanuchi manda fotos/video con las medidas del rótulo grande existente</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FIGURAS PARA PREMIOS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ya presupuestado por Marco Guanuchi (proveedor sin nombre dado)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Listo para enviar a Administración</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ya definido (monto no dictado en la llamada)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Listo para enviar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Mariano lo manda junto con otras cosas para no mandar de a una</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TRONCOS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Contacto pendiente (Marco Jurado se lo pasa a Julio)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sin definir</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Para el reto — se recogen y Logística los lleva hasta el lugar</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sin definir</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Julio todavía no recibió el número de contacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AGUA PARA SENDERISTAS (garrafas)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Contacto de Adrián Rivera (equipo de Cocina), sin confirmar todavía</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Faltan 43 (de 90 necesarias, hay 157... revisar unidad, ver nota)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Deben ser garrafas iguales, mismo color y sabor que el reto anterior</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sin definir</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Adrián dijo que él se encarga y ya sabe dónde comprar, pero falta que confirme presupuesto/contacto real — Julio lo ve mañana 25 ago a las 15:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
+++ b/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Discrepancia sin resolver: faltan 39 según el plan de 65 bolsas nuevas, pero el inventario general pide 90 en total — no se resolvió en la llamada</t>
+          <t>RESUELTO (nota real de Mariano en vivo): la meta correcta es 65 bolsas nuevas, no 90 — el 90 era del inventario viejo. Confirmado: hay 29 bolsas hechas, 34 bolsas vacías (comprar paquete de 100), 26 etiquetas (comprar 39, o sea un paquete de 100).</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amazon o Bricomart/Obramar (a definir)</t>
+          <t>Amazon — cuenta específica de Ruge (no la personal de Julio)</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -729,7 +729,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Julio manda el link elegido para que Mariano arme el presupuesto</t>
+          <t>Julio le pasa el link a Mariano para comprar desde la cuenta de Amazon de Ruge — pedir factura al comprar (para Administración)</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>YA COORDINADO — no hace falta el link de Amazon que había mandado el pastor, ese era para las antorchas en sí</t>
+          <t>Contacto real: Jonathan (vía Marco Guanuchi según la llamada, pero la nota de asignación de tareas de Mariano dice que es David quien le pide a Jonathan — sin resolver quién lo hace finalmente). ~23-24€, ya coordinado, se retira el domingo</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Obramar o Leroy Merlin (a confirmar)</t>
+          <t>Obramat o Leroy Merlin (a confirmar)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1234,7 +1234,146 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Adrián dijo que él se encarga y ya sabe dónde comprar, pero falta que confirme presupuesto/contacto real — Julio lo ve mañana 25 ago a las 15:00</t>
+          <t>Corregido: es David quien tiene que pedirle el contacto/info a Adrián Rivera (según la asignación real de tareas de Mariano) — en la llamada se había dicho que Julio lo vería mañana 25 ago 15:00 si David no lograba contactarlo antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BOLSAS DE BASURA NEGRAS 100L</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A definir — Julio le pregunta a Marco dónde las compró la vez pasada</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sin definir</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Para tapar rótulos grandes (una sola flecha grande)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>9 sept</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Julio repite la compra donde ya se compró antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BOLSAS DE BASURA NEGRAS 50L</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A definir — Julio le pregunta a Marco dónde las compró la vez pasada</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sin definir</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Para tapar rótulos normales/chicos (una sola flecha)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>9 sept</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Julio repite la compra donde ya se compró antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ALARGADOR ELÉCTRICO — LETRERO RUGE ILUMINADO</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Marcos Chiriguaya</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Distinto del alargador general (fila aparte) — específico para el letrero iluminado de Ruge</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>26 ago</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>A confirmar con Marcos Chiriguaya</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Julio se lo pide directo a Marcos Chiriguaya, no a Administración</t>
         </is>
       </c>
     </row>

--- a/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
+++ b/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -590,7 +590,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Marco le escribe a la empresa explicando que las anteriores no funcionaron</t>
+          <t>Marco le escribe a la empresa explicando que las anteriores no funcionaron | Confirmado en el inventario oficial: reto=15 unidades, régimen=ALQUILADO.</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>RESUELTO (nota real de Mariano en vivo): la meta correcta es 65 bolsas nuevas, no 90 — el 90 era del inventario viejo. Confirmado: hay 29 bolsas hechas, 34 bolsas vacías (comprar paquete de 100), 26 etiquetas (comprar 39, o sea un paquete de 100).</t>
+          <t>⚠️ SIN RESOLVER DE VERDAD: en la llamada de hoy decidieron bajar la meta a 65 bolsas, pero el inventario OFICIAL de Marco Jurado (INVENTARIO_2026_RUGE_actualizado_21ago2026.xlsx) sigue diciendo reto=90, sin actualizar. Alguien tiene que avisarle a Marco Jurado del cambio a 65 para que lo corrija ahí — mientras tanto los dos documentos no coinciden.</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>NO — gestión es de Logística directamente, según el inventario oficial (no de Administración)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -836,10 +836,8 @@
           <t>Obramat o Leroy Merlin (a confirmar)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sin definir</t>
-        </is>
+      <c r="C9" t="n">
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -880,7 +878,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Administración (Juliana)</t>
+          <t>YA ES PRESTADO por la Iglesia Impact Valencia (según inventario oficial) — no hay que comprarlo ni pedirlo a Juliana</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -908,12 +906,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>No aplica, ya está prestado</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Probar primero el alargador amarillo grande que ya tienen — puede no estar funcionando</t>
+          <t>Solo falta probar que funcione (el amarillo grande puede estar roto) — no es una gestión de compra</t>
         </is>
       </c>
     </row>
@@ -1374,6 +1372,145 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>Julio se lo pide directo a Marcos Chiriguaya, no a Administración</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TELÉFONO SATELITAL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>⚠️ NO aparece en el inventario oficial de Marco Jurado — se habló en la llamada pero no está cargado ahí. Confirmar con Marco Jurado si falta agregarlo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RÓTULO LUMINOSO INFERIOR "ESPAÑA"</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Levis</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mismo ancho que el rótulo grande existente, más angosto</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sin definir</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>A confirmar</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>⚠️ NO aparece en el inventario oficial</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Puede que Marco Jurado no lo haya cargado todavía — confirmar</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ANTORCHAS DE LED SOLARES</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sin definir</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Faltan 6 (hay 24, reto 30)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ítem separado de las cañas — no se había incluido antes</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>26 ago (según reparto viejo)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Detectado al cruzar con el inventario oficial — no se mencionó en la llamada de hoy</t>
         </is>
       </c>
     </row>

--- a/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
+++ b/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Urgente (presupuesto vence a los 15 días de recibido, 24 ago)</t>
+          <t>Jueves 27 ago 2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>LISTO — Mariano ya tiene el presupuesto, falta enviarlo a Administración</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Urgente, sin fecha exacta</t>
+          <t>Jueves 27 ago 2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sin definir</t>
+          <t>Jueves 27 ago 2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>LISTO — Mariano ya tiene el presupuesto de bolsas + todo el contenido de alimentos, falta enviarlo a Administración. Pendiente</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sin definir</t>
+          <t>Jueves 27 ago 2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>LISTO — Mariano ya tiene el presupuesto de bolsas + todo el contenido de alimentos, falta enviarlo a Administración. Pendiente</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sin definir</t>
+          <t>Jueves 27 ago 2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Resuelto (coordinación)</t>
+          <t>LISTO — Mariano ya tiene el presupuesto, falta enviarlo a Administración</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sin definir</t>
+          <t>Jueves 27 ago 2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sin definir</t>
+          <t>Jueves 27 ago 2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sin definir</t>
+          <t>Jueves 27 ago 2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sin definir</t>
+          <t>Jueves 27 ago 2026</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sin definir, Julio consulta mañana 25 ago</t>
+          <t>Jueves 27 ago 2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sin definir, Julio consulta mañana 25 ago</t>
+          <t>Jueves 27 ago 2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Listo para enviar</t>
+          <t>LISTO — Mariano ya tiene el presupuesto, falta enviarlo a Administración</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sin definir</t>
+          <t>Jueves 27 ago 2026</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sin definir</t>
+          <t>Jueves 27 ago 2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>26 ago</t>
+          <t>Jueves 27 ago 2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sin definir</t>
+          <t>Jueves 27 ago 2026</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>26 ago (según reparto viejo)</t>
+          <t>Jueves 27 ago 2026</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">

--- a/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
+++ b/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Presupuesto Logística" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Presupuesto Logística" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amazon (junto con bolsas de basura negras, para un solo pedido)</t>
+          <t>Amazon — https://www.amazon.es/dp/B0CQ2CWX1Y</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente — no se pudo consultar el precio de Amazon desde este sistema (dominio bloqueado), confirmar precio con Mariano</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Hay 34 actuales — comprar de más porque algunas vienen malas/no se pegan bien</t>
+          <t>Hay 34 actuales — comprar de más porque algunas vienen malas/no se pegan bien. Necesitamos paquete de 100 (link de Amazon compartido 28 ago).</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Obramat o Leroy Merlin (a confirmar)</t>
+          <t>Amazon — https://www.amazon.es/dp/B0BHQDDXJ7</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -851,7 +851,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente — no se pudo consultar el precio de Amazon desde este sistema (dominio bloqueado), confirmar precio con Mariano</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>No se consiguió el reto anterior por buscarla a último momento</t>
+          <t>No se consiguió el reto anterior por buscarla a último momento. Link de Amazon compartido 28 ago 2026.</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Por confirmar — un lugar en Valencia manda presupuesto el 25 ago</t>
+          <t>Talleres Fandos S.L. (Fandos Rent) — sede Paterna, Valencia</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -931,32 +931,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Debe soportar 1.000kg. Mariano prefiere pick-up 4x4 (Ford Ranger/Hilux/Amarok/Isuzu) por sobre un camión largo tipo Iveco — más manejable en tramos difíciles de montaña</t>
+          <t>IVECO Daily caja abierta, 3 plazas, MMA 3.500kg, carga máx. ~1.000kg. Exteriores 6,87m largo. Zona carga 4,40m x 2,03m. 1.000km incluidos, 0,18€+IVA km extra. Depósito fianza 300€. Presupuesto Nº 0325/26.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Presupuesto llega el 25 ago a primera hora</t>
+          <t>Alquiler del 30/09/2026 11:00 al 05/10/2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>667,01€ IVA incluido</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Administración</t>
+          <t>Depósito 300€ + alquiler — forma de pago sin especificar en el presupuesto, confirmar con Fandos Rent (638 81 96 48)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>LISTO — presupuesto real recibido, falta enviarlo a Administración</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>David también evalúa opciones en Alicante/Castellón si en Valencia no aparece pick-up</t>
+          <t>PDF de presupuesto real recibido 28 ago 2026, cargado en Drive. Válido 10 días desde el 25 ago (emisión) — revisar vencimiento si se demora la aprobación. Contacto: Pepito Pérez, 638 81 96 48.</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Levis</t>
+          <t>VIS Publicidad (+34 694 27 89 08)</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mismo ancho que el rótulo grande ya existente, más angosto en largo</t>
+          <t>Vinilo con corte. El cliente (GOTIR/Ruge) envía el diseño.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jueves 27 ago 2026</t>
+          <t>Sin fecha límite dada en el presupuesto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>317,00€ sin IVA + IVA 21% (66,57€) = 383,57€ total</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A confirmar</t>
+          <t>50% al aprobar + 50% en la entrega, efectivo o transferencia a ES89 2100 5513 4802 0022 3174 (Caixabank, a nombre de Levington Guerrero)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>LISTO — presupuesto real recibido, falta enviarlo a Administración</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Marco Guanuchi manda fotos/video con las medidas del rótulo grande existente</t>
+          <t>PDF de presupuesto real recibido 28 ago 2026, cargado en Drive.</t>
         </is>
       </c>
     </row>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ya presupuestado por Marco Guanuchi (proveedor sin nombre dado)</t>
+          <t>Ya presupuestado por Marco Guanuchi (impresión 3D)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Impresión 3D, 100mm por figura, material PLA (800g total para las 5), incluye posprocesado y pintado/acabado. 18€ por figura.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Listo para enviar a Administración</t>
+          <t>Sin fecha límite dada en el presupuesto</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ya definido (monto no dictado en la llamada)</t>
+          <t>90,00€ (18€ x 5 figuras)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>LISTO — Mariano ya tiene el presupuesto, falta enviarlo a Administración</t>
+          <t>LISTO — presupuesto real recibido, falta enviarlo a Administración</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Mariano lo manda junto con otras cosas para no mandar de a una</t>
+          <t>⚠️ El inventario oficial de Marco Jurado pide 7 figuras (reto 50 hombres), este presupuesto es solo para 5 — confirmar con Mariano si faltan 2 más por cotizar o si el reto real bajó a 5. PDF cargado en Drive.</t>
         </is>
       </c>
     </row>
@@ -1425,45 +1425,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RÓTULO LUMINOSO INFERIOR "ESPAÑA"</t>
+          <t>RÓTULO LUMINOSO INFERIOR "ESPAÑA" (fila duplicada)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Levis</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mismo ancho que el rótulo grande existente, más angosto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jueves 27 ago 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>A confirmar</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>⚠️ NO aparece en el inventario oficial</t>
+          <t>Ver fila 14 — mismo ítem, presupuesto ya cargado ahí</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Puede que Marco Jurado no lo haya cargado todavía — confirmar</t>
+          <t>Fila duplicada del ítem de la fila 14, se deja vacía para no contar dos veces en el presupuesto total.</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1477,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sin definir</t>
+          <t>Amazon — https://www.amazon.es/dp/B0DS2GM9QR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Faltan 6 (hay 24, reto 30)</t>
+          <t>6 (mínimo de compra del paquete — solo se necesitan 3, faltan 6 según inventario oficial)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1495,7 +1497,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente — no se pudo consultar el precio de Amazon desde este sistema (dominio bloqueado), confirmar precio con Mariano</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1510,7 +1512,54 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Detectado al cruzar con el inventario oficial — no se mencionó en la llamada de hoy</t>
+          <t>Detectado al cruzar con el inventario oficial (faltan 6 de 30, hay 24). Mariano solo necesita 3, pero el paquete de Amazon tiene mínimo 6 — coincide con el faltante real, se compran las 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ALIMENTO PARA BOLSA DE PROVISIONES (contenido, 10 productos)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Listado de compra (documento generado a partir de nota manuscrita)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>65 bolsas x contenido de cada producto (ver detalle)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MINIS RELLENO: Caja 8 paquetes — 1,95€ | GALLETA MANZANA: Caja 8 paquetes — 1,65€ | GALLETA CHOCO BLANCO: Caja 6 paquetes — 1,30€ | BARRA FRUTO SECO: Caja 6 paquetes — 1,65€ | CARAMELO BLANCO: Bolsa 45 unidades — 1,60€ | COLA CAO: Caja 50 sobres — 19,99€ | SNICKERS: Bolsa 5 unidades — 4,25€ | SOBRES TANG: Caja 30 unidades — 0,79€/unidad | RIN TIN MARUCHAN: Paquete 5 packs — 1,99€ | ATÚN GIRASOL DIDI: Pack 4 unidades — 1,99€</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sin fecha límite dada en el listado</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ver precio por producto en el detalle — falta sumar el total según cantidad real de bolsas (65)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>LISTO — listado real recibido, falta calcular el total y enviarlo a Administración</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Es el contenido que va DENTRO de cada bolsa de provisiones (fila 5 son las bolsas vacías). Documento recibido 28 ago 2026, cargado en Drive.</t>
         </is>
       </c>
     </row>

--- a/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
+++ b/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pendiente — no se pudo consultar el precio de Amazon desde este sistema (dominio bloqueado), confirmar precio con Mariano</t>
+          <t>10,99€ (paquete de 100, 229x305mm, 0,11€/unidad) — marca NefLaca, vendedor Paper Print Mart</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Hay 34 actuales — comprar de más porque algunas vienen malas/no se pegan bien. Necesitamos paquete de 100 (link de Amazon compartido 28 ago).</t>
+          <t>Hay 34 actuales — comprar de más porque algunas vienen malas/no se pegan bien. Link: https://www.amazon.es/dp/B0CQ2CWX1Y — precio confirmado por Mariano (captura) 28 ago 2026.</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pendiente — no se pudo consultar el precio de Amazon desde este sistema (dominio bloqueado), confirmar precio con Mariano</t>
+          <t>11,99€ (rollo 5cm x 10m) — marca YXSF</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>No se consiguió el reto anterior por buscarla a último momento. Link de Amazon compartido 28 ago 2026.</t>
+          <t>⚠️ El producto del link es AMARILLA FLUORESCENTE, no plateada como dice el nombre original del ítem — confirmar con Mariano si el color no importa o si hace falta buscar otra. Cantidad necesaria original: 2 — si son 2 rollos, total 23,98€. Link: https://www.amazon.es/dp/B0BHQDDXJ7 — precio confirmado por Mariano (captura) 28 ago 2026.</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PDF de presupuesto real recibido 28 ago 2026, cargado en Drive. Válido 10 días desde el 25 ago (emisión) — revisar vencimiento si se demora la aprobación. Contacto: Pepito Pérez, 638 81 96 48.</t>
+          <t>PDF de presupuesto real recibido 28 ago 2026. Drive: https://drive.google.com/file/d/1wAsPjYeVI59B_aIMXqs-A4_4vj3f-t46/view?usp=drive_link. Válido 10 días desde el 25 ago (emisión) — revisar vencimiento si se demora la aprobación. Contacto: Pepito Pérez, 638 81 96 48.</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PDF de presupuesto real recibido 28 ago 2026, cargado en Drive.</t>
+          <t>PDF de presupuesto real recibido 28 ago 2026. Drive: https://drive.google.com/file/d/1iK3L8s8NCgFfXymTNTYn1B94iH_TraiX/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>⚠️ El inventario oficial de Marco Jurado pide 7 figuras (reto 50 hombres), este presupuesto es solo para 5 — confirmar con Mariano si faltan 2 más por cotizar o si el reto real bajó a 5. PDF cargado en Drive.</t>
+          <t>⚠️ El inventario oficial de Marco Jurado pide 7 figuras (reto 50 hombres), este presupuesto es solo para 5 — confirmar con Mariano si faltan 2 más por cotizar o si el reto real bajó a 5. PDF de presupuesto real recibido 28 ago 2026. Drive: https://drive.google.com/file/d/1v1CwPe1KVW6PnS5_VsIPvtY9ueIjWAoZ/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pendiente — no se pudo consultar el precio de Amazon desde este sistema (dominio bloqueado), confirmar precio con Mariano</t>
+          <t>23,99€ (pack de 6, 4,00€/unidad) — marca FIFlying, con cupón 15% disponible</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Detectado al cruzar con el inventario oficial (faltan 6 de 30, hay 24). Mariano solo necesita 3, pero el paquete de Amazon tiene mínimo 6 — coincide con el faltante real, se compran las 6.</t>
+          <t>Detectado al cruzar con el inventario oficial (faltan 6 de 30, hay 24). Mariano solo necesita 3, pero el paquete de Amazon tiene mínimo 6 — coincide con el faltante real, se compran las 6. Link: https://www.amazon.es/dp/B0DS2GM9QR — precio confirmado por Mariano (captura) 28 ago 2026. Hay cupón de 15% aplicable, revisar si baja el precio final.</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Es el contenido que va DENTRO de cada bolsa de provisiones (fila 5 son las bolsas vacías). Documento recibido 28 ago 2026, cargado en Drive.</t>
+          <t>Es el contenido que va DENTRO de cada bolsa de provisiones (fila 5 son las bolsas vacías). Documento recibido 28 ago 2026. Drive: https://drive.google.com/file/d/12TJiNe615jcy5EZkLY8JUfWSoKXg3XCx/view?usp=drive_link</t>
         </is>
       </c>
     </row>

--- a/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
+++ b/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Empresa ya contactada (misma del reto anterior, nombre sin confirmar)</t>
+          <t>Autocares Azahar S.L. — Lorena Castillo (964539073 / 626190593), Camí de la Travessa 3, 12540 Vila-real</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -518,17 +518,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>55 asientos, presupuesto con descuento negociado</t>
+          <t>Bus 55 plazas, servicio de ida y vuelta. 01 oct: salida desde Manises, traslado a Xodos. 04 oct: salida de Xodos, traslado a Manises.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jueves 27 ago 2026</t>
+          <t>Jueves 27 ago 2026 (venció, pendiente confirmación con Administración)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>~1.197€ (sin confirmar exacto, Marco lo dijo con dudas)</t>
+          <t>1.190,00€ IVA incluido</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>LISTO — Mariano ya tiene el presupuesto, falta enviarlo a Administración</t>
+          <t>LISTO — presupuesto real confirmado 28 ago 2026, falta enviarlo a Administración</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Correo con presupuesto ya recibido por Mariano, falta abrirlo y confirmar cifra exacta</t>
+          <t>Precio exacto confirmado 28 ago 2026 (antes se estimaba ~1.197€ "con dudas") — cifra real: 1.190,00€.</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Levis</t>
+          <t>Levis (mismo proveedor del rótulo luminoso)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nombre + talla + logo Ruge, hecha en computadora/impresora (se descartó escribir a mano con rotulador)</t>
+          <t>Nombre + talla + logo Ruge, hecha en computadora/impresora</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>0€ — GRATIS, Levis lo regala por hacer el cartel/rótulo luminoso con ellos</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>A confirmar si entra en el mismo presupuesto que el rótulo luminoso</t>
+          <t>No aplica — no requiere pago</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>LISTO — confirmado 28 ago 2026, sin costo, no requiere autorización de Administración</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Julio pide cotización y tiempos de entrega a Levis</t>
+          <t>Confirmado por Mariano 28 ago 2026: es un regalo de Levis por encargarles el rótulo luminoso (fila 14), no un ítem de presupuesto aparte.</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>90,00€ (18€ x 5 figuras)</t>
+          <t>Pendiente — el presupuesto de 90€ era para 5 figuras, Mariano confirmó que hace falta pedir presupuesto nuevo por 7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>LISTO — presupuesto real recibido, falta enviarlo a Administración</t>
+          <t>Pendiente — falta el presupuesto nuevo por 7 unidades antes de mandarlo a Administración</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>⚠️ El inventario oficial de Marco Jurado pide 7 figuras (reto 50 hombres), este presupuesto es solo para 5 — confirmar con Mariano si faltan 2 más por cotizar o si el reto real bajó a 5. PDF de presupuesto real recibido 28 ago 2026. Drive: https://drive.google.com/file/d/1v1CwPe1KVW6PnS5_VsIPvtY9ueIjWAoZ/view?usp=drive_link</t>
+          <t>Confirmado por Mariano 28 ago 2026: el inventario oficial pide 7 figuras, hay que volver a cotizar (el presupuesto de 90€/5 unidades ya no sirve tal cual). PDF del presupuesto viejo (5 unidades), como referencia de precio unitario (18€/figura): https://drive.google.com/file/d/1v1CwPe1KVW6PnS5_VsIPvtY9ueIjWAoZ/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -1197,17 +1197,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Contacto de Adrián Rivera (equipo de Cocina), sin confirmar todavía</t>
+          <t>Distribuciones Pascual (C/Carmen Herrero Penella 1-3-21, 46470 Catarroja)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faltan 43 (de 90 necesarias, hay 157... revisar unidad, ver nota)</t>
+          <t>50 garrafas (necesarias: faltan 43 de 90, este presupuesto cubre el redondeo a 50)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Deben ser garrafas iguales, mismo color y sabor que el reto anterior</t>
+          <t>Agua 5L, marca "La Serreta". Presupuesto Nº 2500004.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>54,45€ total (49,50€ base + 10% dto. ya aplicado + IVA 10%: 4,95€) — 0,99€/unidad antes de IVA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Administración</t>
+          <t>Administración — forma de pago/domiciliación no especificada en el presupuesto</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>LISTO — presupuesto real recibido 28 ago 2026, falta enviarlo a Administración</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Corregido: es David quien tiene que pedirle el contacto/info a Adrián Rivera (según la asignación real de tareas de Mariano) — en la llamada se había dicho que Julio lo vería mañana 25 ago 15:00 si David no lograba contactarlo antes</t>
+          <t>Presupuesto emitido 26 ago 2026, válido según vencimiento indicado (26/08/2026 — revisar si sigue vigente al momento de aprobar).</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>65 bolsas x contenido de cada producto (ver detalle)</t>
+          <t>Ver cantidades faltantes por producto en el detalle (cruzado contra inventario oficial)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MINIS RELLENO: Caja 8 paquetes — 1,95€ | GALLETA MANZANA: Caja 8 paquetes — 1,65€ | GALLETA CHOCO BLANCO: Caja 6 paquetes — 1,30€ | BARRA FRUTO SECO: Caja 6 paquetes — 1,65€ | CARAMELO BLANCO: Bolsa 45 unidades — 1,60€ | COLA CAO: Caja 50 sobres — 19,99€ | SNICKERS: Bolsa 5 unidades — 4,25€ | SOBRES TANG: Caja 30 unidades — 0,79€/unidad | RIN TIN MARUCHAN: Paquete 5 packs — 1,99€ | ATÚN GIRASOL DIDI: Pack 4 unidades — 1,99€</t>
+          <t>Cruzado 28 ago 2026 contra el inventario oficial de Marco Jurado (INVENTARIO_2026_RUGE_actualizado_21ago2026.xlsx), columnas Stock actual / Reto 50 hombres:
+- MINIS RELLENO: stock 20, reto 90, faltan 70 → comprar 9 cajas de 8 paq (72u) x 1,95€ = 17,55€
+- GALLETA MANZANA: stock 6, reto 90, faltan 84 → comprar 11 cajas de 8 paq (88u) x 1,65€ = 18,15€
+- GALLETA CHOCO BLANCO: stock 0, reto 90, faltan 90 → comprar 15 cajas de 6 paq (90u) x 1,30€ = 19,50€
+- BARRA FRUTO SECO: stock 42, reto 180 (¡ojo, este reto es 180, no 90!), faltan 138 → comprar 23 cajas de 6 paq (138u) x 1,65€ = 37,95€
+- CARAMELO BLANCO: ⚠️ no se pudo cruzar con certeza — el oficial tiene "CARAMELOS SURTIDOS" (stock 2 paquetes, reto 5 paquetes) pero el nombre y la unidad no coinciden con "bolsa 45 und" del listado — confirmar con Marco Jurado si es el mismo ítem
+- COLA CAO: stock 24, reto 90, faltan 66 sobres → comprar 2 cajas de 50 sobres (100u) x 19,99€ = 39,98€
+- SNICKERS: stock 7, reto 90, faltan 83 → comprar 17 bolsas de 5u (85u) x 4,25€ = 72,25€
+- SOBRES TANG: stock 10, reto 90, faltan 80 → comprar 3 cajas de 30u (90u) x 0,79€/u = 71,10€
+- RIN TIN MARUCHAN: stock 58, reto 180, faltan 122 → comprar 25 packs de 5 (125u) x 1,99€ = 49,75€
+- ATÚN GIRASOL DIDI: stock 32, reto 90, faltan 58 → comprar 15 packs de 4u (60u) x 1,99€ = 29,85€</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1544,7 +1554,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ver precio por producto en el detalle — falta sumar el total según cantidad real de bolsas (65)</t>
+          <t>~356,08€ estimado (suma de las cantidades sugeridas arriba, sin contar CARAMELO BLANCO — sin resolver)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1554,12 +1564,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>LISTO — listado real recibido, falta calcular el total y enviarlo a Administración</t>
+          <t>LISTO — cruzado contra el inventario oficial 28 ago 2026, falta resolver CARAMELO BLANCO y enviar a Administración</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Es el contenido que va DENTRO de cada bolsa de provisiones (fila 5 son las bolsas vacías). Documento recibido 28 ago 2026. Drive: https://drive.google.com/file/d/12TJiNe615jcy5EZkLY8JUfWSoKXg3XCx/view?usp=drive_link</t>
+          <t>Es el contenido que va DENTRO de cada bolsa de provisiones (fila 5 son las bolsas vacías). Cantidades sugeridas en paquetes/cajas — Julio/Marco confirman si prefieren otro tamaño de compra. Drive: https://drive.google.com/file/d/12TJiNe615jcy5EZkLY8JUfWSoKXg3XCx/view?usp=drive_link</t>
         </is>
       </c>
     </row>

--- a/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
+++ b/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
@@ -585,12 +585,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente — Marco espera que Juliana le pase el número de contacto de la empresa (misma que teléfono satelital)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Marco le escribe a la empresa explicando que las anteriores no funcionaron | Confirmado en el inventario oficial: reto=15 unidades, régimen=ALQUILADO.</t>
+          <t>Marco le escribe a la empresa explicando que las anteriores no funcionaron | Confirmado en el inventario oficial: reto=15 unidades, régimen=ALQUILADO. ⚠️ 28 ago 2026: Marco está esperando que Juliana le mande el número de contacto — hay que recordarle a Marco que se lo pida.</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>⚠️ SIN RESOLVER DE VERDAD: en la llamada de hoy decidieron bajar la meta a 65 bolsas, pero el inventario OFICIAL de Marco Jurado (INVENTARIO_2026_RUGE_actualizado_21ago2026.xlsx) sigue diciendo reto=90, sin actualizar. Alguien tiene que avisarle a Marco Jurado del cambio a 65 para que lo corrija ahí — mientras tanto los dos documentos no coinciden.</t>
+          <t>Aclarado 28 ago 2026 por Mariano: hacen falta 90 en total (coincide con el inventario oficial), pero ya tenemos algunas en stock — por eso la cifra de compra rondaba los 65, no es una discrepancia real entre documentos.</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Faltan 4 de las 52 necesarias (hay 48) — son de madera/tronquito</t>
+          <t>Son de madera/tronquito. Aclarado 28 ago 2026: son TODOS los platos que faltan (no solo 4) — falta confirmar la cantidad exacta con Marcos Chiriguaya.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>David confirma stock real en la web de Tedi antes de comprar. Richard graba el nombre DESPUÉS de comprarlos, no antes</t>
+          <t>Aclarado 28 ago 2026: David tiene que confirmar precio y disponibilidad directo con Marcos Chiriguaya (no directo con Tedi). Richard graba el nombre DESPUÉS de comprarlos, no antes.</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ya presupuestado por Marco Guanuchi (impresión 3D)</t>
+          <t>Marco Guanuchi (pendiente de él, no de Julio) — presupuesto anterior de 5 unidades como referencia</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Confirmado por Mariano 28 ago 2026: el inventario oficial pide 7 figuras, hay que volver a cotizar (el presupuesto de 90€/5 unidades ya no sirve tal cual). PDF del presupuesto viejo (5 unidades), como referencia de precio unitario (18€/figura): https://drive.google.com/file/d/1v1CwPe1KVW6PnS5_VsIPvtY9ueIjWAoZ/view?usp=drive_link</t>
+          <t>Confirmado por Mariano 28 ago 2026: el inventario oficial pide 7 figuras y este pendiente es de Marco Guanuchi. Hay que volver a cotizar (el presupuesto de 90€/5 unidades ya no sirve tal cual, queda como referencia de precio: 18€/figura). PDF viejo: https://drive.google.com/file/d/1v1CwPe1KVW6PnS5_VsIPvtY9ueIjWAoZ/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>EN CURSO — Marco Jurado ya le pasó el número de contacto a Julio, que ya está contactando</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Julio todavía no recibió el número de contacto</t>
+          <t>Actualizado 28 ago 2026: Marco Jurado ya le pasó el contacto a Julio y Julio ya lo está contactando — ya no está bloqueado esperando el número.</t>
         </is>
       </c>
     </row>
@@ -1383,42 +1383,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>Misma empresa que las radios VHF (fila 3)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pendiente — Marco espera el número de contacto de Juliana, mismo caso que las radios VHF</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>⚠️ NO aparece en el inventario oficial de Marco Jurado — se habló en la llamada pero no está cargado ahí. Confirmar con Marco Jurado si falta agregarlo.</t>
+          <t>⚠️ NO aparece en el inventario oficial de Marco Jurado — se habló en la llamada pero no está cargado ahí. Confirmar con Marco Jurado si falta agregarlo. 28 ago 2026: es la misma empresa de las radios VHF — Marco espera que Juliana le pase el número.</t>
         </is>
       </c>
     </row>

--- a/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
+++ b/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Julio le pasa el link a Mariano para comprar desde la cuenta de Amazon de Ruge — pedir factura al comprar (para Administración)</t>
+          <t>⚠️ 28 ago 2026: el inventario oficial de Marco Jurado dice que la comisión de revisión es COCINA, no Logística — contradice lo registrado en la llamada del 24 ago ("gestión es de Logística directamente"). Confirmar con Marco Jurado cuál es la correcta antes de asignarlo a alguien.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Actualizado 28 ago 2026: Marco Jurado ya le pasó el contacto a Julio y Julio ya lo está contactando — ya no está bloqueado esperando el número.</t>
+          <t>Actualizado 28 ago 2026: Marco Jurado ya le pasó el contacto a Julio y Julio ya lo está contactando — ya no está bloqueado esperando el número. ⚠️ Nota: la comisión de revisión oficial es LOGÍSTICA Y EVENTOS (Eventos debería ejecutar), pero como Julio ya arrancó la gestión en la práctica, se deja con él en vez de redirigir a mitad de camino.</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Julio repite la compra donde ya se compró antes</t>
+          <t>⚠️ 28 ago 2026: comisión de revisión oficial es LOGÍSTICA Y EVENTOS — según la regla ya confirmada por Marco Jurado, la segunda comisión (Eventos, Mauricio/Cristian) es quien gestiona/ejecuta, Logística solo corrobora. Reasignado de Julio a Eventos.</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Julio repite la compra donde ya se compró antes</t>
+          <t>⚠️ 28 ago 2026: comisión de revisión oficial es LOGÍSTICA Y EVENTOS — según la regla ya confirmada por Marco Jurado, la segunda comisión (Eventos, Mauricio/Cristian) es quien gestiona/ejecuta, Logística solo corrobora. Reasignado de Julio a Eventos.</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Julio se lo pide directo a Marcos Chiriguaya, no a Administración</t>
+          <t>⚠️ 28 ago 2026: comisión de revisión oficial es LOGÍSTICA Y EVENTOS — Eventos (Mauricio/Cristian) gestiona/ejecuta, Julio solo corrobora. Reasignado de Julio a Eventos.</t>
         </is>
       </c>
     </row>

--- a/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
+++ b/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
@@ -1105,7 +1105,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Marco Guanuchi (pendiente de él, no de Julio) — presupuesto anterior de 5 unidades como referencia</t>
+          <t>Marco Guanuchi (impresión 3D)</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pendiente — el presupuesto de 90€ era para 5 figuras, Mariano confirmó que hace falta pedir presupuesto nuevo por 7</t>
+          <t>91,00€ (13,00€ x 7 figuras)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pendiente — falta el presupuesto nuevo por 7 unidades antes de mandarlo a Administración</t>
+          <t>LISTO — presupuesto real por 7 unidades recibido 28 ago 2026, falta enviarlo a Administración</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Confirmado por Mariano 28 ago 2026: el inventario oficial pide 7 figuras y este pendiente es de Marco Guanuchi. Hay que volver a cotizar (el presupuesto de 90€/5 unidades ya no sirve tal cual, queda como referencia de precio: 18€/figura). PDF viejo: https://drive.google.com/file/d/1v1CwPe1KVW6PnS5_VsIPvtY9ueIjWAoZ/view?usp=drive_link</t>
+          <t>Confirmado: cotización nueva por 7 unidades, más barata por unidad que la de 5 (13€ vs 18€/figura). Falta que Mariano suba el PDF a su Drive y pase el link.</t>
         </is>
       </c>
     </row>

--- a/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
+++ b/mariano-os/areas/ministerio/recursos/Presupuesto_Logistica_Ruge_24ago2026.xlsx
@@ -816,12 +816,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>CASI LISTO — David ya consiguió y grabó los platos que faltaban, solo falta que envíen la factura</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Aclarado 28 ago 2026: David tiene que confirmar precio y disponibilidad directo con Marcos Chiriguaya (no directo con Tedi). Richard graba el nombre DESPUÉS de comprarlos, no antes.</t>
+          <t>Actualizado 28 ago 2026: David ya consiguió los platos que faltaban y ya están grabados con "RUGE". Queda pendiente únicamente que envíen la factura de esos platos.</t>
         </is>
       </c>
     </row>
